--- a/output/quickfixclose3_portfolio_daily.xlsx
+++ b/output/quickfixclose3_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>364,452.53</t>
+          <t>374,069.92</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+264.45%</t>
+          <t>+274.07%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>377,304  (+277.30%)</t>
+          <t>387,360  (+287.36%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,000  (12.9 pts of return)</t>
+          <t>5,107  (13.3 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20.5x</t>
+          <t>21.2x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+5.87R  (best +25.73R)</t>
+          <t>+5.81R  (best +25.73R)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9,498  (+5.87%)</t>
+          <t>9,499  (+5.81%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5627,24 +5627,72 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>364452.53</v>
+        <v>364559.39</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>0</v>
+        <v>2671.5</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>364452.53</v>
+        <v>361887.9</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures exit_close (+54,644)</t>
-        </is>
-      </c>
+          <t>US_Dollar_Index_Futures exit_close (+54,644)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>374069.92</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>374069.92</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures exit_close (+9,511)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>374069.92</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>374069.92</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10067,7 @@
         <v>104553.02</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>552960.6</v>
+        <v>553164.26</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -10043,14 +10091,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="G86" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.04</v>
+        <v>3.56</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>366283.8</v>
@@ -10058,15 +10114,15 @@
       <c r="J86" s="5" t="n">
         <v>5091.34</v>
       </c>
-      <c r="K86" s="6" t="n">
-        <v>-203.65</v>
+      <c r="K86" s="7" t="n">
+        <v>18125.19</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>448407.58</v>
+        <v>571289.4399999999</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose3_portfolio_daily.xlsx
+++ b/output/quickfixclose3_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>374,069.92</t>
+          <t>374,049.75</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+274.07%</t>
+          <t>+274.05%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,107  (13.3 pts of return)</t>
+          <t>5,127  (13.3 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5694,6 +5694,62 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>374069.92</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>11110.25</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>362959.67</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 3,741); Nasdaq_100_E_mini short (risk 3,703); S_P_500_E_mini short (risk 3,666)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>374049.75</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>374049.75</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 3,630)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5706,7 +5762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10126,6 +10182,178 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>571289.4399999999</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>7940.92</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-27.57</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>571248.42</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>563348.52</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>7830.54</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>571275.99</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>555517.97</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>7721.7</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>571246.79</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>547796.28</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>7614.37</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>-13.02</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>571276.4300000001</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixclose3_portfolio_daily.xlsx
+++ b/output/quickfixclose3_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>374,049.75</t>
+          <t>370,377.87</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+274.05%</t>
+          <t>+270.38%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>387,360  (+287.36%)</t>
+          <t>383,601  (+283.60%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,127  (13.3 pts of return)</t>
+          <t>5,170  (13.2 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21.2x</t>
+          <t>20.9x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.0%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,612  (-1.29%)</t>
+          <t>-1,654  (-1.29%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5727,26 +5727,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>374049.75</v>
+        <v>374069.92</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>14739.85</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>359330.07</v>
+      </c>
+      <c r="E190" t="n">
+        <v>4</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 3,630)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>370377.87</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>374049.75</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>370377.87</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 3,630)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 3,593); NY_Palladium_Futures short (risk 3,557)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-3,654); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10217,7 +10245,7 @@
         <v>-27.57</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>571248.42</v>
+        <v>563545.6800000001</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -10260,7 +10288,7 @@
         <v>-0.43</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>571275.99</v>
+        <v>563622.58</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -10303,7 +10331,7 @@
         <v>-1.63</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>571246.79</v>
+        <v>563544.04</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -10327,14 +10355,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G90" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I90" s="5" t="n">
         <v>547796.28</v>
@@ -10343,12 +10379,98 @@
         <v>7614.37</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>-13.02</v>
+        <v>-7666.43</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>571276.4300000001</v>
+        <v>563623.01</v>
       </c>
       <c r="M90" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>540181.91</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>7508.53</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>-20.29</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>563602.28</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>532673.38</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>7404.16</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>-29.04</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>563573.25</v>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
